--- a/data/crops/rothc_support/annual_crops_reduced_tillage_rothc_scenarios.xlsx
+++ b/data/crops/rothc_support/annual_crops_reduced_tillage_rothc_scenarios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://worldwildlifefund-my.sharepoint.com/personal/cristobal_loyola_wwfus_org/Documents/Documents/203. Python projects/SBTN_Test/data/crops/rothc_support/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{10CA9DB5-EBAF-437F-9133-092C57B088DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{78FFA68D-946B-4192-B238-13758B0DF3B1}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="8_{10CA9DB5-EBAF-437F-9133-092C57B088DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA8AF3BF-90E7-4299-87C8-6C8C50D7AA6C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{5393C2E3-8FA9-4147-8B5B-2520450A0FB5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="150">
   <si>
     <t>crop_name</t>
   </si>
@@ -89,18 +89,6 @@
     <t>residue_runs</t>
   </si>
   <si>
-    <t>spam_crop_raster</t>
-  </si>
-  <si>
-    <t>spam_all_fp</t>
-  </si>
-  <si>
-    <t>spam_irr_fp</t>
-  </si>
-  <si>
-    <t>spam_rf_fp</t>
-  </si>
-  <si>
     <t>force_new_file</t>
   </si>
   <si>
@@ -113,42 +101,6 @@
     <t>irr</t>
   </si>
   <si>
-    <t>../LEAFs/SOC/rasters</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_ron_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_BARL_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_BARL_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_BARL_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_irr_roff_irr_monthly.tif</t>
-  </si>
-  <si>
     <t>irr_ron_rt</t>
   </si>
   <si>
@@ -185,305 +137,412 @@
     <t>Wheat</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_rf_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_rf_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Barley_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_rf_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Barley_rf_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_ron_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_MAIZ_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_MAIZ_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_MAIZ_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_irr_roff_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_ron_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_RAPE_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_RAPE_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_RAPE_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_irr_roff_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_ron_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SORG_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SORG_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SORG_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_irr_roff_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_ron_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_WHEA_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_WHEA_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_WHEA_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Wheat_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_irr_roff_irr_monthly.tif</t>
-  </si>
-  <si>
     <t>irr_rt</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Irrigated_cotton.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Cotton_irr_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Cotton_irr_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Cotton_irr_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_COTT_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_COTT_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_COTT_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Soybeans.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Soybean_irr_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Soybean_irr_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Soybean_irr_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SOYB_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SOYB_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SOYB_R.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Irrigated_Sunflower.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sunflower_irr_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sunflower_irr_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sunflower_irr_irr_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SUNF_I.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SUNF_A.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/spam2020V2r0_global_yield/spam2020_V2r0_global_Y_SUNF_R.tif</t>
-  </si>
-  <si>
     <t>rf_rt</t>
   </si>
   <si>
-    <t>../data/land_use/lu_Rainfed_cotton.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Cotton_rf_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Cotton_rf_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_rf_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Maize_rf_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Maize_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_rf_ron_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Rapeseed_rf_ron_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Rapeseed_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_rf_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sorghum_rf_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sorghum_residues_removed_from_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Soybeans.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Soybean_rf_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Soybean_rf_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Sunflower.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sunflower_rf_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Sunflower_rf_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_left_on_the_field.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_rf_roff_pet_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/crops/rothc_support/Wheat_rf_roff_pc_monthly.tif</t>
-  </si>
-  <si>
-    <t>../data/land_use/lu_Rainfed_Wheat_residues_removed_from_the_field.tif</t>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_ron_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_roff_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_roff_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_irr_roff_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>ylds_crop_raster</t>
+  </si>
+  <si>
+    <t>ylds_all_fp</t>
+  </si>
+  <si>
+    <t>ylds_irr_fp</t>
+  </si>
+  <si>
+    <t>ylds_rf_fp</t>
+  </si>
+  <si>
+    <t>ylds_src</t>
+  </si>
+  <si>
+    <t>outlier_strategy</t>
+  </si>
+  <si>
+    <t>percentile_bound</t>
+  </si>
+  <si>
+    <t>apply_local_zscore</t>
+  </si>
+  <si>
+    <t>apply_soc_clip</t>
+  </si>
+  <si>
+    <t>soc_global_percentile_cap</t>
+  </si>
+  <si>
+    <t>max_annual_soc_gain</t>
+  </si>
+  <si>
+    <t>max_soc_tc_ha</t>
+  </si>
+  <si>
+    <t>yield_global_percentile_cap</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BRL.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BRL.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BRL.WSR.tif</t>
+  </si>
+  <si>
+    <t>GAEZ</t>
+  </si>
+  <si>
+    <t>log_winsor</t>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFFF9E64"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>1.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF89DDFF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFA9B1D6"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FFFF9E64"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>99.0</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="7"/>
+        <color rgb="FF89DDFF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Carrot_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Carrot_irr_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Carrot_irr_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Carrot_irr_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RTS.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RTS.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RTS.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Cotton_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Cotton_rf_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Cotton_rf_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COT.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COT.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.COT.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_ron_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.MZE.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.MZE.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.MZE.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_roff_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_roff_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_irr_roff_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Maize_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_rf_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Maize_rf_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_ron_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RSD.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RSD.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RSD.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_roff_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_roff_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_irr_roff_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Rapeseed_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_rf_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Rapeseed_rf_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_ron_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SRG.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SRG.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SRG.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sorghum_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_roff_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_roff_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sorghum_irr_roff_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Soybean_irr_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Soybean_irr_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Soybean_irr_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SOY.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SOY.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SOY.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Soybean_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Soybean_rf_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Soybean_rf_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_irr.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sunflower_irr_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sunflower_irr_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sunflower_irr_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SFL.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SFL.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SFL.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Sunflower_rf.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sunflower_rf_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Sunflower_rf_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_ron_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.WHE.WST.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.WHE.WSI.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.WHE.WSR.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_irr_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_roff_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_roff_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_irr_roff_irr_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Wheat_rf_roff.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_rf_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Wheat_rf_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\land_use\FAO_GAEZ/lu_gaez_Barley_rf_ron.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_rf_ron_pet_monthly.tif</t>
+  </si>
+  <si>
+    <t>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\rothc_support\FAO_GAEZ\Barley_rf_ron_pc_monthly.tif</t>
+  </si>
+  <si>
+    <t>../LEAFs/SOC/rasters_clipped/reduced_tillage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -505,16 +564,47 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFA9B1D6"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="7"/>
+      <color rgb="FFFF7EDB"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFFF9E64"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF89DDFF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -522,16 +612,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -866,16 +989,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A18CCF2-0471-428A-B57D-47F27A4FBA50}">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.1796875" customWidth="1"/>
     <col min="7" max="7" width="48.453125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="133.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -925,55 +1050,82 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="V1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB1" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="AD1" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="D2" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>36</v>
       </c>
       <c r="E2">
         <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G2" t="str">
         <f>+"RothC results for year 2030 for "&amp;A2&amp;"_"&amp;D2&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Barley_irr_ron_rt in ton C/ha</v>
       </c>
-      <c r="H2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" t="s">
-        <v>28</v>
+      <c r="H2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -984,56 +1136,78 @@
       <c r="P2">
         <v>100</v>
       </c>
-      <c r="Q2" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" t="s">
-        <v>29</v>
-      </c>
-      <c r="T2" t="s">
-        <v>31</v>
+      <c r="Q2" t="str">
+        <f>+S2</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BRL.WSI.tif</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
       </c>
+      <c r="V2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W2" t="s">
+        <v>59</v>
+      </c>
+      <c r="X2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA2">
+        <v>99.5</v>
+      </c>
+      <c r="AD2">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" t="s">
-        <v>37</v>
       </c>
       <c r="E3">
         <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G3" t="str">
         <f>+"RothC results for year 2030 for "&amp;A3&amp;"_"&amp;D3&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Barley_irr_roff_rt in ton C/ha</v>
       </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="H3" s="4" t="s">
         <v>35</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="N3" t="b">
         <v>1</v>
@@ -1044,53 +1218,75 @@
       <c r="P3">
         <v>100</v>
       </c>
-      <c r="Q3" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" t="s">
-        <v>30</v>
-      </c>
-      <c r="S3" t="s">
-        <v>29</v>
-      </c>
-      <c r="T3" t="s">
-        <v>31</v>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3" si="0">+S3</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.BRL.WSI.tif</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="U3" t="b">
         <v>0</v>
       </c>
+      <c r="V3" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W3" t="s">
+        <v>59</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y3" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA3">
+        <v>99.5</v>
+      </c>
+      <c r="AD3">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G4" t="str">
         <f>+"RothC results for year 2030 for "&amp;A4&amp;"_"&amp;D4&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Barley_rf_ron_rt in ton C/ha</v>
       </c>
-      <c r="H4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" t="s">
-        <v>50</v>
+      <c r="H4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="N4" t="b">
         <v>1</v>
@@ -1101,53 +1297,74 @@
       <c r="P4">
         <v>100</v>
       </c>
-      <c r="Q4" t="s">
-        <v>31</v>
-      </c>
-      <c r="R4" t="s">
-        <v>30</v>
-      </c>
-      <c r="S4" t="s">
-        <v>29</v>
-      </c>
-      <c r="T4" t="s">
-        <v>31</v>
+      <c r="Q4" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T4" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="U4" t="b">
         <v>0</v>
       </c>
+      <c r="V4" t="s">
+        <v>58</v>
+      </c>
+      <c r="W4" t="s">
+        <v>59</v>
+      </c>
+      <c r="X4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y4" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA4">
+        <v>99.5</v>
+      </c>
+      <c r="AD4">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E5">
         <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G5" t="str">
         <f>+"RothC results for year 2030 for "&amp;A5&amp;"_"&amp;D5&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Barley_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H5" t="s">
-        <v>51</v>
-      </c>
-      <c r="I5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J5" t="s">
-        <v>53</v>
+      <c r="H5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>148</v>
       </c>
       <c r="N5" t="b">
         <v>1</v>
@@ -1158,56 +1375,77 @@
       <c r="P5">
         <v>100</v>
       </c>
-      <c r="Q5" t="s">
-        <v>31</v>
-      </c>
-      <c r="R5" t="s">
-        <v>30</v>
-      </c>
-      <c r="S5" t="s">
-        <v>29</v>
-      </c>
-      <c r="T5" t="s">
-        <v>31</v>
+      <c r="Q5" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T5" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="U5" t="b">
         <v>0</v>
       </c>
+      <c r="V5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W5" t="s">
+        <v>59</v>
+      </c>
+      <c r="X5" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y5" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA5">
+        <v>99.5</v>
+      </c>
+      <c r="AD5">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="E6">
         <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" ref="G6:G27" si="0">+"RothC results for year 2030 for "&amp;A6&amp;"_"&amp;D6&amp;" in ton C/ha"</f>
+        <f t="shared" ref="G6:G27" si="1">+"RothC results for year 2030 for "&amp;A6&amp;"_"&amp;D6&amp;" in ton C/ha"</f>
         <v>RothC results for year 2030 for Cotton_irr_rt in ton C/ha</v>
       </c>
-      <c r="H6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I6" t="s">
-        <v>100</v>
-      </c>
-      <c r="J6" t="s">
-        <v>101</v>
-      </c>
-      <c r="K6" t="s">
-        <v>102</v>
+      <c r="H6" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
@@ -1218,56 +1456,79 @@
       <c r="P6">
         <v>100</v>
       </c>
-      <c r="Q6" t="s">
-        <v>103</v>
-      </c>
-      <c r="R6" t="s">
-        <v>104</v>
-      </c>
-      <c r="S6" t="s">
-        <v>103</v>
-      </c>
-      <c r="T6" t="s">
-        <v>105</v>
+      <c r="Q6" t="str">
+        <f t="shared" ref="Q5:Q6" si="2">+S6</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RTS.WSI.tif</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="T6" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
       </c>
+      <c r="V6" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W6" t="s">
+        <v>59</v>
+      </c>
+      <c r="X6" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA6">
+        <v>99.5</v>
+      </c>
+      <c r="AD6">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
-        <v>38</v>
-      </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Cotton_rf_rt in ton C/ha</v>
       </c>
-      <c r="H7" t="s">
-        <v>121</v>
-      </c>
-      <c r="I7" t="s">
-        <v>122</v>
-      </c>
-      <c r="J7" t="s">
-        <v>123</v>
-      </c>
+      <c r="H7" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="6"/>
       <c r="N7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="b">
         <v>0</v>
@@ -1275,56 +1536,77 @@
       <c r="P7">
         <v>100</v>
       </c>
-      <c r="Q7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R7" t="s">
-        <v>104</v>
-      </c>
-      <c r="S7" t="s">
-        <v>103</v>
-      </c>
-      <c r="T7" t="s">
-        <v>105</v>
+      <c r="Q7" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="T7" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="U7" t="b">
         <v>0</v>
       </c>
+      <c r="V7" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W7" t="s">
+        <v>59</v>
+      </c>
+      <c r="X7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y7" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA7">
+        <v>99.5</v>
+      </c>
+      <c r="AD7">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E8">
         <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Maize_irr_ron_rt in ton C/ha</v>
       </c>
-      <c r="H8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I8" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" t="s">
-        <v>56</v>
-      </c>
-      <c r="K8" t="s">
-        <v>57</v>
+      <c r="H8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="N8" t="b">
         <v>1</v>
@@ -1335,56 +1617,78 @@
       <c r="P8">
         <v>100</v>
       </c>
-      <c r="Q8" t="s">
+      <c r="Q8" t="str">
+        <f t="shared" ref="Q8:Q9" si="3">+S8</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.MZE.WSI.tif</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="R8" t="s">
+      <c r="W8" t="s">
         <v>59</v>
       </c>
-      <c r="S8" t="s">
-        <v>58</v>
-      </c>
-      <c r="T8" t="s">
+      <c r="X8" t="s">
         <v>60</v>
       </c>
-      <c r="U8" t="b">
-        <v>0</v>
+      <c r="Y8" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>99.5</v>
+      </c>
+      <c r="AD8">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Maize_irr_roff_rt in ton C/ha</v>
       </c>
-      <c r="H9" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-      <c r="K9" t="s">
-        <v>64</v>
+      <c r="H9" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="N9" t="b">
         <v>1</v>
@@ -1395,56 +1699,78 @@
       <c r="P9">
         <v>100</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q9" t="str">
+        <f t="shared" si="3"/>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.MZE.WSI.tif</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U9" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="R9" t="s">
+      <c r="W9" t="s">
         <v>59</v>
       </c>
-      <c r="S9" t="s">
-        <v>58</v>
-      </c>
-      <c r="T9" t="s">
+      <c r="X9" t="s">
         <v>60</v>
       </c>
-      <c r="U9" t="b">
-        <v>0</v>
+      <c r="Y9" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA9">
+        <v>99.5</v>
+      </c>
+      <c r="AD9">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="C10" t="s">
-        <v>38</v>
-      </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E10">
         <v>14</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Maize_rf_ron_rt in ton C/ha</v>
       </c>
-      <c r="H10" t="s">
-        <v>124</v>
-      </c>
-      <c r="I10" t="s">
-        <v>125</v>
-      </c>
-      <c r="J10" t="s">
-        <v>126</v>
+      <c r="H10" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="N10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" t="b">
         <v>0</v>
@@ -1452,56 +1778,77 @@
       <c r="P10">
         <v>100</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="Q10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="T10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U10" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W10" t="s">
+        <v>59</v>
+      </c>
+      <c r="X10" t="s">
         <v>60</v>
       </c>
-      <c r="R10" t="s">
-        <v>59</v>
-      </c>
-      <c r="S10" t="s">
-        <v>58</v>
-      </c>
-      <c r="T10" t="s">
-        <v>60</v>
-      </c>
-      <c r="U10" t="b">
-        <v>0</v>
+      <c r="Y10" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA10">
+        <v>99.5</v>
+      </c>
+      <c r="AD10">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E11">
         <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Maize_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" t="s">
-        <v>125</v>
-      </c>
-      <c r="J11" t="s">
-        <v>126</v>
+      <c r="H11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="N11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O11" t="b">
         <v>0</v>
@@ -1509,59 +1856,80 @@
       <c r="P11">
         <v>100</v>
       </c>
-      <c r="Q11" t="s">
+      <c r="Q11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="T11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="U11" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W11" t="s">
+        <v>59</v>
+      </c>
+      <c r="X11" t="s">
         <v>60</v>
       </c>
-      <c r="R11" t="s">
-        <v>59</v>
-      </c>
-      <c r="S11" t="s">
-        <v>58</v>
-      </c>
-      <c r="T11" t="s">
-        <v>60</v>
-      </c>
-      <c r="U11" t="b">
-        <v>0</v>
+      <c r="Y11" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA11">
+        <v>99.5</v>
+      </c>
+      <c r="AD11">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E12">
         <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Rapeseed_irr_ron_rt in ton C/ha</v>
       </c>
-      <c r="H12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I12" t="s">
-        <v>66</v>
-      </c>
-      <c r="J12" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" t="s">
-        <v>68</v>
+      <c r="H12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="N12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12" t="b">
         <v>0</v>
@@ -1569,59 +1937,81 @@
       <c r="P12">
         <v>100</v>
       </c>
-      <c r="Q12" t="s">
-        <v>69</v>
-      </c>
-      <c r="R12" t="s">
-        <v>70</v>
-      </c>
-      <c r="S12" t="s">
-        <v>69</v>
-      </c>
-      <c r="T12" t="s">
-        <v>71</v>
+      <c r="Q12" t="str">
+        <f t="shared" ref="Q12:Q13" si="4">+S12</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RSD.WSI.tif</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T12" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="U12" t="b">
         <v>0</v>
       </c>
+      <c r="V12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W12" t="s">
+        <v>59</v>
+      </c>
+      <c r="X12" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y12" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA12">
+        <v>99.5</v>
+      </c>
+      <c r="AD12">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E13">
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Rapeseed_irr_roff_rt in ton C/ha</v>
       </c>
-      <c r="H13" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" t="s">
-        <v>74</v>
-      </c>
-      <c r="K13" t="s">
-        <v>75</v>
+      <c r="H13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="N13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O13" t="b">
         <v>0</v>
@@ -1629,56 +2019,78 @@
       <c r="P13">
         <v>100</v>
       </c>
-      <c r="Q13" t="s">
-        <v>69</v>
-      </c>
-      <c r="R13" t="s">
-        <v>70</v>
-      </c>
-      <c r="S13" t="s">
-        <v>69</v>
-      </c>
-      <c r="T13" t="s">
-        <v>71</v>
+      <c r="Q13" t="str">
+        <f t="shared" si="4"/>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.RSD.WSI.tif</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T13" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="U13" t="b">
         <v>0</v>
       </c>
+      <c r="V13" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W13" t="s">
+        <v>59</v>
+      </c>
+      <c r="X13" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y13" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>99.5</v>
+      </c>
+      <c r="AD13">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>38</v>
-      </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Rapeseed_rf_ron_rt in ton C/ha</v>
       </c>
-      <c r="H14" t="s">
-        <v>128</v>
-      </c>
-      <c r="I14" t="s">
-        <v>129</v>
-      </c>
-      <c r="J14" t="s">
-        <v>130</v>
+      <c r="H14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="N14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O14" t="b">
         <v>0</v>
@@ -1686,56 +2098,77 @@
       <c r="P14">
         <v>100</v>
       </c>
-      <c r="Q14" t="s">
-        <v>71</v>
-      </c>
-      <c r="R14" t="s">
-        <v>70</v>
-      </c>
-      <c r="S14" t="s">
-        <v>69</v>
-      </c>
-      <c r="T14" t="s">
-        <v>71</v>
+      <c r="Q14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T14" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="U14" t="b">
         <v>0</v>
       </c>
+      <c r="V14" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W14" t="s">
+        <v>59</v>
+      </c>
+      <c r="X14" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y14" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA14">
+        <v>99.5</v>
+      </c>
+      <c r="AD14">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" t="s">
         <v>22</v>
       </c>
-      <c r="C15" t="s">
-        <v>38</v>
-      </c>
       <c r="D15" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E15">
         <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Rapeseed_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I15" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" t="s">
-        <v>130</v>
+      <c r="H15" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="N15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="b">
         <v>0</v>
@@ -1743,59 +2176,80 @@
       <c r="P15">
         <v>100</v>
       </c>
-      <c r="Q15" t="s">
-        <v>71</v>
-      </c>
-      <c r="R15" t="s">
-        <v>70</v>
-      </c>
-      <c r="S15" t="s">
-        <v>69</v>
-      </c>
-      <c r="T15" t="s">
-        <v>71</v>
+      <c r="Q15" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="U15" t="b">
         <v>0</v>
       </c>
+      <c r="V15" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W15" t="s">
+        <v>59</v>
+      </c>
+      <c r="X15" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y15" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA15">
+        <v>99.5</v>
+      </c>
+      <c r="AD15">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D16" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E16">
         <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sorghum_irr_ron_rt in ton C/ha</v>
       </c>
-      <c r="H16" t="s">
-        <v>76</v>
-      </c>
-      <c r="I16" t="s">
-        <v>77</v>
-      </c>
-      <c r="J16" t="s">
-        <v>78</v>
-      </c>
-      <c r="K16" t="s">
-        <v>79</v>
+      <c r="H16" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>104</v>
       </c>
       <c r="N16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O16" t="b">
         <v>0</v>
@@ -1803,59 +2257,81 @@
       <c r="P16">
         <v>100</v>
       </c>
-      <c r="Q16" t="s">
-        <v>80</v>
-      </c>
-      <c r="R16" t="s">
-        <v>81</v>
-      </c>
-      <c r="S16" t="s">
-        <v>80</v>
-      </c>
-      <c r="T16" t="s">
-        <v>82</v>
+      <c r="Q16" t="str">
+        <f t="shared" ref="Q16:Q17" si="5">+S16</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SRG.WSI.tif</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T16" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="U16" t="b">
         <v>0</v>
       </c>
+      <c r="V16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W16" t="s">
+        <v>59</v>
+      </c>
+      <c r="X16" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y16" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA16">
+        <v>99.5</v>
+      </c>
+      <c r="AD16">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E17">
         <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sorghum_irr_roff_rt in ton C/ha</v>
       </c>
-      <c r="H17" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" t="s">
-        <v>84</v>
-      </c>
-      <c r="J17" t="s">
-        <v>85</v>
-      </c>
-      <c r="K17" t="s">
-        <v>86</v>
+      <c r="H17" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="N17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O17" t="b">
         <v>0</v>
@@ -1863,56 +2339,78 @@
       <c r="P17">
         <v>100</v>
       </c>
-      <c r="Q17" t="s">
-        <v>80</v>
-      </c>
-      <c r="R17" t="s">
-        <v>81</v>
-      </c>
-      <c r="S17" t="s">
-        <v>80</v>
-      </c>
-      <c r="T17" t="s">
-        <v>82</v>
+      <c r="Q17" t="str">
+        <f t="shared" si="5"/>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SRG.WSI.tif</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T17" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="U17" t="b">
         <v>0</v>
       </c>
+      <c r="V17" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W17" t="s">
+        <v>59</v>
+      </c>
+      <c r="X17" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA17">
+        <v>99.5</v>
+      </c>
+      <c r="AD17">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="s">
-        <v>38</v>
-      </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E18">
         <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G18" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sorghum_rf_ron_rt in ton C/ha</v>
       </c>
-      <c r="H18" t="s">
-        <v>132</v>
-      </c>
-      <c r="I18" t="s">
-        <v>133</v>
-      </c>
-      <c r="J18" t="s">
-        <v>134</v>
+      <c r="H18" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="N18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O18" t="b">
         <v>0</v>
@@ -1920,56 +2418,77 @@
       <c r="P18">
         <v>100</v>
       </c>
-      <c r="Q18" t="s">
-        <v>82</v>
-      </c>
-      <c r="R18" t="s">
-        <v>81</v>
-      </c>
-      <c r="S18" t="s">
-        <v>80</v>
-      </c>
-      <c r="T18" t="s">
-        <v>82</v>
+      <c r="Q18" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T18" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="U18" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V18" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W18" t="s">
+        <v>59</v>
+      </c>
+      <c r="X18" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA18">
+        <v>99.5</v>
+      </c>
+      <c r="AD18">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" t="s">
-        <v>38</v>
-      </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E19">
         <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G19" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sorghum_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H19" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" t="s">
-        <v>133</v>
-      </c>
-      <c r="J19" t="s">
-        <v>134</v>
+      <c r="H19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>110</v>
       </c>
       <c r="N19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O19" t="b">
         <v>0</v>
@@ -1977,59 +2496,80 @@
       <c r="P19">
         <v>100</v>
       </c>
-      <c r="Q19" t="s">
-        <v>82</v>
-      </c>
-      <c r="R19" t="s">
-        <v>81</v>
-      </c>
-      <c r="S19" t="s">
-        <v>80</v>
-      </c>
-      <c r="T19" t="s">
-        <v>82</v>
+      <c r="Q19" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="T19" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="U19" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="V19" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W19" t="s">
+        <v>59</v>
+      </c>
+      <c r="X19" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA19">
+        <v>99.5</v>
+      </c>
+      <c r="AD19">
+        <v>99.5</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D20" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="E20">
         <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G20" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Soybean_irr_rt in ton C/ha</v>
       </c>
-      <c r="H20" t="s">
-        <v>106</v>
-      </c>
-      <c r="I20" t="s">
-        <v>107</v>
-      </c>
-      <c r="J20" t="s">
-        <v>108</v>
-      </c>
-      <c r="K20" t="s">
-        <v>109</v>
+      <c r="H20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="N20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O20" t="b">
         <v>0</v>
@@ -2037,56 +2577,78 @@
       <c r="P20">
         <v>100</v>
       </c>
-      <c r="Q20" t="s">
-        <v>110</v>
-      </c>
-      <c r="R20" t="s">
-        <v>111</v>
-      </c>
-      <c r="S20" t="s">
-        <v>110</v>
-      </c>
-      <c r="T20" t="s">
-        <v>112</v>
+      <c r="Q20" t="str">
+        <f t="shared" ref="Q20" si="6">+S20</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SOY.WSI.tif</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="T20" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="U20" t="b">
         <v>0</v>
       </c>
+      <c r="V20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W20" t="s">
+        <v>59</v>
+      </c>
+      <c r="X20" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA20">
+        <v>99.5</v>
+      </c>
+      <c r="AD20">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
         <v>22</v>
       </c>
-      <c r="C21" t="s">
-        <v>38</v>
-      </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>33</v>
       </c>
       <c r="E21">
         <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Soybean_rf_rt in ton C/ha</v>
       </c>
-      <c r="H21" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" t="s">
-        <v>138</v>
+      <c r="H21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="N21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="b">
         <v>0</v>
@@ -2094,59 +2656,80 @@
       <c r="P21">
         <v>100</v>
       </c>
-      <c r="Q21" t="s">
-        <v>112</v>
-      </c>
-      <c r="R21" t="s">
-        <v>111</v>
-      </c>
-      <c r="S21" t="s">
-        <v>110</v>
-      </c>
-      <c r="T21" t="s">
-        <v>112</v>
+      <c r="Q21" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="T21" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="U21" t="b">
         <v>0</v>
       </c>
+      <c r="V21" t="s">
+        <v>58</v>
+      </c>
+      <c r="W21" t="s">
+        <v>59</v>
+      </c>
+      <c r="X21" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA21">
+        <v>99.5</v>
+      </c>
+      <c r="AD21">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D22" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="E22">
         <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sunflower_irr_rt in ton C/ha</v>
       </c>
-      <c r="H22" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" t="s">
-        <v>114</v>
-      </c>
-      <c r="J22" t="s">
-        <v>115</v>
-      </c>
-      <c r="K22" t="s">
-        <v>116</v>
+      <c r="H22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K22" s="5" t="s">
+        <v>125</v>
       </c>
       <c r="N22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O22" t="b">
         <v>0</v>
@@ -2154,56 +2737,78 @@
       <c r="P22">
         <v>100</v>
       </c>
-      <c r="Q22" t="s">
-        <v>117</v>
-      </c>
-      <c r="R22" t="s">
-        <v>118</v>
-      </c>
-      <c r="S22" t="s">
-        <v>117</v>
-      </c>
-      <c r="T22" t="s">
-        <v>119</v>
+      <c r="Q22" t="str">
+        <f t="shared" ref="Q22" si="7">+S22</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.SFL.WSI.tif</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T22" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="U22" t="b">
         <v>0</v>
       </c>
+      <c r="V22" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W22" t="s">
+        <v>59</v>
+      </c>
+      <c r="X22" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA22">
+        <v>99.5</v>
+      </c>
+      <c r="AD22">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" t="s">
         <v>22</v>
       </c>
-      <c r="C23" t="s">
-        <v>38</v>
-      </c>
       <c r="D23" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E23">
         <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Sunflower_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H23" t="s">
-        <v>139</v>
-      </c>
-      <c r="I23" t="s">
-        <v>140</v>
-      </c>
-      <c r="J23" t="s">
-        <v>141</v>
+      <c r="H23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>131</v>
       </c>
       <c r="N23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O23" t="b">
         <v>0</v>
@@ -2211,59 +2816,80 @@
       <c r="P23">
         <v>100</v>
       </c>
-      <c r="Q23" t="s">
-        <v>119</v>
-      </c>
-      <c r="R23" t="s">
-        <v>118</v>
-      </c>
-      <c r="S23" t="s">
-        <v>117</v>
-      </c>
-      <c r="T23" t="s">
-        <v>119</v>
+      <c r="Q23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="U23" t="b">
         <v>0</v>
       </c>
+      <c r="V23" t="s">
+        <v>58</v>
+      </c>
+      <c r="W23" t="s">
+        <v>59</v>
+      </c>
+      <c r="X23" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA23">
+        <v>99.5</v>
+      </c>
+      <c r="AD23">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E24">
         <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Wheat_irr_ron_rt in ton C/ha</v>
       </c>
-      <c r="H24" t="s">
-        <v>87</v>
-      </c>
-      <c r="I24" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" t="s">
-        <v>89</v>
-      </c>
-      <c r="K24" t="s">
-        <v>90</v>
+      <c r="H24" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="N24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O24" t="b">
         <v>0</v>
@@ -2271,59 +2897,81 @@
       <c r="P24">
         <v>100</v>
       </c>
-      <c r="Q24" t="s">
-        <v>91</v>
-      </c>
-      <c r="R24" t="s">
-        <v>92</v>
-      </c>
-      <c r="S24" t="s">
-        <v>91</v>
-      </c>
-      <c r="T24" t="s">
-        <v>93</v>
+      <c r="Q24" t="str">
+        <f t="shared" ref="Q24:Q25" si="8">+S24</f>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.WHE.WSI.tif</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="T24" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="U24" t="b">
         <v>0</v>
       </c>
+      <c r="V24" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W24" t="s">
+        <v>59</v>
+      </c>
+      <c r="X24" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA24">
+        <v>99.5</v>
+      </c>
+      <c r="AD24">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="E25">
         <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Wheat_irr_roff_rt in ton C/ha</v>
       </c>
-      <c r="H25" t="s">
-        <v>94</v>
-      </c>
-      <c r="I25" t="s">
-        <v>95</v>
-      </c>
-      <c r="J25" t="s">
-        <v>96</v>
-      </c>
-      <c r="K25" t="s">
-        <v>97</v>
+      <c r="H25" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="N25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O25" t="b">
         <v>0</v>
@@ -2331,56 +2979,78 @@
       <c r="P25">
         <v>100</v>
       </c>
-      <c r="Q25" t="s">
-        <v>91</v>
-      </c>
-      <c r="R25" t="s">
-        <v>92</v>
-      </c>
-      <c r="S25" t="s">
-        <v>91</v>
-      </c>
-      <c r="T25" t="s">
-        <v>93</v>
+      <c r="Q25" t="str">
+        <f t="shared" si="8"/>
+        <v>C:\Users\loyola\OneDrive - World Wildlife Fund, Inc\Documents\203. Python projects\SBTN_Test\data\crops\FAO_GAEZ\YIELDS\GAEZ-V5.RES06-YLD.WHE.WSI.tif</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="U25" t="b">
         <v>0</v>
       </c>
+      <c r="V25" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="W25" t="s">
+        <v>59</v>
+      </c>
+      <c r="X25" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA25">
+        <v>99.5</v>
+      </c>
+      <c r="AD25">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" t="s">
         <v>22</v>
       </c>
-      <c r="C26" t="s">
-        <v>38</v>
-      </c>
       <c r="D26" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="E26">
         <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Wheat_rf_ron_rt in ton C/ha</v>
       </c>
-      <c r="H26" t="s">
-        <v>142</v>
-      </c>
-      <c r="I26" t="s">
+      <c r="H26" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J26" t="s">
+      <c r="I26" s="3" t="s">
         <v>144</v>
       </c>
+      <c r="J26" s="5" t="s">
+        <v>145</v>
+      </c>
       <c r="N26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O26" t="b">
         <v>0</v>
@@ -2388,56 +3058,77 @@
       <c r="P26">
         <v>100</v>
       </c>
-      <c r="Q26" t="s">
-        <v>93</v>
-      </c>
-      <c r="R26" t="s">
-        <v>92</v>
-      </c>
-      <c r="S26" t="s">
-        <v>91</v>
-      </c>
-      <c r="T26" t="s">
-        <v>93</v>
+      <c r="Q26" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="T26" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="U26" t="b">
         <v>0</v>
       </c>
+      <c r="V26" t="s">
+        <v>58</v>
+      </c>
+      <c r="W26" t="s">
+        <v>59</v>
+      </c>
+      <c r="X26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA26">
+        <v>99.5</v>
+      </c>
+      <c r="AD26">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
         <v>22</v>
       </c>
-      <c r="C27" t="s">
-        <v>38</v>
-      </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="E27">
         <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>149</v>
       </c>
       <c r="G27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>RothC results for year 2030 for Wheat_rf_roff_rt in ton C/ha</v>
       </c>
-      <c r="H27" t="s">
+      <c r="H27" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J27" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="I27" t="s">
-        <v>143</v>
-      </c>
-      <c r="J27" t="s">
-        <v>144</v>
-      </c>
       <c r="N27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="b">
         <v>0</v>
@@ -2445,32 +3136,53 @@
       <c r="P27">
         <v>100</v>
       </c>
-      <c r="Q27" t="s">
-        <v>93</v>
-      </c>
-      <c r="R27" t="s">
-        <v>92</v>
-      </c>
-      <c r="S27" t="s">
-        <v>91</v>
-      </c>
-      <c r="T27" t="s">
-        <v>93</v>
+      <c r="Q27" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>138</v>
       </c>
       <c r="U27" t="b">
         <v>0</v>
       </c>
+      <c r="V27" t="s">
+        <v>58</v>
+      </c>
+      <c r="W27" t="s">
+        <v>59</v>
+      </c>
+      <c r="X27" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA27">
+        <v>99.5</v>
+      </c>
+      <c r="AD27">
+        <v>99.5</v>
+      </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
     </row>
   </sheetData>
